--- a/login_id.xlsx
+++ b/login_id.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0896DB1D-A39B-4435-B5F1-B0003A024526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A04453A-9994-4C1F-A5D7-46248231420F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
     <t>로그인유형</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +76,38 @@
   </si>
   <si>
     <t>심우승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿈비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강민성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이대훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조승연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장진영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -537,39 +569,81 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>

--- a/login_id.xlsx
+++ b/login_id.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\대시보드\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ABAD93-BF40-4237-960C-FD396C3F4D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C9FF4A-661C-49AC-B225-EF707FCD0FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="131">
   <si>
     <t>로그인유형</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,29 +99,13 @@
     <t>조승연</t>
   </si>
   <si>
-    <t>조승연</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장진영</t>
   </si>
   <si>
-    <t>장진영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>정지현</t>
   </si>
   <si>
-    <t>정지현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>정지영</t>
-  </si>
-  <si>
-    <t>정지영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>관리자</t>
@@ -852,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -871,12 +855,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -885,12 +869,12 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -899,12 +883,12 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -913,12 +897,12 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -927,12 +911,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -941,7 +925,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -952,10 +936,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -966,10 +950,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -980,10 +964,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -994,10 +978,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1008,10 +992,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1022,10 +1006,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1036,234 +1020,234 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1271,13 +1255,13 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1285,13 +1269,13 @@
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1299,13 +1283,13 @@
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1313,13 +1297,13 @@
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1327,13 +1311,13 @@
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1341,13 +1325,13 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1355,13 +1339,13 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1369,13 +1353,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1383,13 +1367,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1397,13 +1381,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1411,13 +1395,13 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1425,13 +1409,13 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1439,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1453,13 +1437,13 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1467,13 +1451,13 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1481,13 +1465,13 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1495,13 +1479,13 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1509,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1523,13 +1507,13 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1537,13 +1521,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1551,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1565,13 +1549,13 @@
         <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1579,13 +1563,13 @@
         <v>8</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1593,13 +1577,13 @@
         <v>8</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1607,13 +1591,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1621,13 +1605,13 @@
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1635,13 +1619,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1649,13 +1633,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1663,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>13</v>
@@ -1677,13 +1661,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1691,13 +1675,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1705,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
@@ -1719,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>15</v>
@@ -1733,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
@@ -1747,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
@@ -1761,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1775,13 +1759,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1789,13 +1773,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1803,13 +1787,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1817,13 +1801,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1831,13 +1815,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1845,13 +1829,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1859,13 +1843,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1873,13 +1857,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1887,13 +1871,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1901,13 +1885,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1915,13 +1899,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1929,13 +1913,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1943,13 +1927,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1957,13 +1941,13 @@
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -1971,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -1985,13 +1969,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -1999,13 +1983,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2189,102 +2173,46 @@
       <c r="D112" s="2"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
@@ -2855,48 +2783,6 @@
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="2"/>
-      <c r="B215" s="2"/>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="2"/>
-      <c r="B216" s="2"/>
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A217" s="2"/>
-      <c r="B217" s="2"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A218" s="2"/>
-      <c r="B218" s="2"/>
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A219" s="2"/>
-      <c r="B219" s="2"/>
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A220" s="2"/>
-      <c r="B220" s="2"/>
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
